--- a/data/processed/san_data.xlsx
+++ b/data/processed/san_data.xlsx
@@ -1816,7 +1816,7 @@
         <v>1.39</v>
       </c>
       <c r="G47" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="48">
@@ -3352,7 +3352,7 @@
         <v>84.31</v>
       </c>
       <c r="G99" t="n">
-        <v>80.26000000000001</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="100">
@@ -5856,7 +5856,7 @@
         <v>10.71</v>
       </c>
       <c r="G183" t="n">
-        <v>8.869999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="184">
@@ -6187,7 +6187,7 @@
         <v>0.98</v>
       </c>
       <c r="G194" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="195">
@@ -6940,7 +6940,7 @@
         <v>18.43</v>
       </c>
       <c r="G219" t="n">
-        <v>11.12</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="220">
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>635.1900000000001</v>
+        <v>634.95</v>
       </c>
       <c r="G277" t="n">
-        <v>614.7</v>
+        <v>371.21</v>
       </c>
     </row>
     <row r="278">
@@ -8710,7 +8710,7 @@
         <v>332.46</v>
       </c>
       <c r="G281" t="n">
-        <v>311.6</v>
+        <v>316.33</v>
       </c>
     </row>
     <row r="282">
@@ -8772,7 +8772,7 @@
         <v>17.46</v>
       </c>
       <c r="G283" t="n">
-        <v>12.76</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="284">
@@ -9950,7 +9950,7 @@
         <v>18.65</v>
       </c>
       <c r="G321" t="n">
-        <v>16.42</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="322">
@@ -10012,7 +10012,7 @@
         <v>18.68</v>
       </c>
       <c r="G323" t="n">
-        <v>16.37</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="324">
@@ -10260,7 +10260,7 @@
         <v>80.05</v>
       </c>
       <c r="G331" t="n">
-        <v>38.34</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="332">
@@ -10322,7 +10322,7 @@
         <v>48.05</v>
       </c>
       <c r="G333" t="n">
-        <v>8.42</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="334">
@@ -10384,7 +10384,7 @@
         <v>42.05</v>
       </c>
       <c r="G335" t="n">
-        <v>15.98</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="336">
@@ -10446,7 +10446,7 @@
         <v>30.05</v>
       </c>
       <c r="G337" t="n">
-        <v>7.36</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="338">
@@ -10938,7 +10938,7 @@
         <v>291.95</v>
       </c>
       <c r="G353" t="n">
-        <v>279.55</v>
+        <v>280.02</v>
       </c>
     </row>
     <row r="354">
@@ -11186,7 +11186,7 @@
         <v>293.95</v>
       </c>
       <c r="G361" t="n">
-        <v>285.12</v>
+        <v>285.36</v>
       </c>
     </row>
     <row r="362">
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>25.05</v>
+        <v>28.96</v>
       </c>
       <c r="G382" t="n">
-        <v>8.27</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="383">
@@ -11907,10 +11907,10 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>25.05</v>
+        <v>28.96</v>
       </c>
       <c r="G385" t="n">
-        <v>8.27</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="386">
@@ -14527,7 +14527,7 @@
         <v>8</v>
       </c>
       <c r="G470" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="471">
@@ -14589,7 +14589,7 @@
         <v>8</v>
       </c>
       <c r="G472" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="473">
@@ -15110,7 +15110,7 @@
         <v>20</v>
       </c>
       <c r="G489" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="490">
@@ -15172,7 +15172,7 @@
         <v>20</v>
       </c>
       <c r="G491" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="492">
@@ -15234,7 +15234,7 @@
         <v>20</v>
       </c>
       <c r="G493" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="494">
@@ -16074,7 +16074,7 @@
         <v>24</v>
       </c>
       <c r="G521" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="522">
@@ -16136,7 +16136,7 @@
         <v>24</v>
       </c>
       <c r="G523" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="524">
@@ -16818,7 +16818,7 @@
         <v>8</v>
       </c>
       <c r="G545" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="546">
@@ -16880,7 +16880,7 @@
         <v>8</v>
       </c>
       <c r="G547" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="548">
@@ -17554,7 +17554,7 @@
         <v>17</v>
       </c>
       <c r="G569" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="570">
@@ -17616,7 +17616,7 @@
         <v>17</v>
       </c>
       <c r="G571" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="572">
@@ -17678,7 +17678,7 @@
         <v>17</v>
       </c>
       <c r="G573" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="574">
@@ -17740,7 +17740,7 @@
         <v>108</v>
       </c>
       <c r="G575" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="576">
@@ -17802,7 +17802,7 @@
         <v>108</v>
       </c>
       <c r="G577" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="578">
@@ -17864,7 +17864,7 @@
         <v>108</v>
       </c>
       <c r="G579" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="580">
@@ -17926,7 +17926,7 @@
         <v>12</v>
       </c>
       <c r="G581" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="582">
@@ -17988,7 +17988,7 @@
         <v>12</v>
       </c>
       <c r="G583" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="584">
@@ -18050,7 +18050,7 @@
         <v>12</v>
       </c>
       <c r="G585" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="586">
@@ -20101,7 +20101,7 @@
         <v>16</v>
       </c>
       <c r="G652" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="653">
@@ -20163,7 +20163,7 @@
         <v>16</v>
       </c>
       <c r="G654" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="655">
@@ -20225,7 +20225,7 @@
         <v>16</v>
       </c>
       <c r="G656" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="657">
@@ -22082,7 +22082,7 @@
         <v>14</v>
       </c>
       <c r="G717" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="718">
@@ -22144,7 +22144,7 @@
         <v>14</v>
       </c>
       <c r="G719" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="720">
@@ -22206,7 +22206,7 @@
         <v>14</v>
       </c>
       <c r="G721" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="722">
@@ -23364,7 +23364,7 @@
         <v>1.35</v>
       </c>
       <c r="G759" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="760">
@@ -23488,7 +23488,7 @@
         <v>3.96</v>
       </c>
       <c r="G763" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="764">
@@ -24374,10 +24374,10 @@
         </is>
       </c>
       <c r="F792" t="n">
-        <v>249.02</v>
+        <v>274.02</v>
       </c>
       <c r="G792" t="n">
-        <v>241.11</v>
+        <v>241.61</v>
       </c>
     </row>
     <row r="793">
@@ -25006,7 +25006,7 @@
         <v>1.94</v>
       </c>
       <c r="G813" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="814">
@@ -25217,7 +25217,7 @@
         <v>0.58</v>
       </c>
       <c r="G820" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="821">
@@ -25341,7 +25341,7 @@
         <v>141.9</v>
       </c>
       <c r="G824" t="n">
-        <v>135.68</v>
+        <v>136.98</v>
       </c>
     </row>
     <row r="825">
@@ -25490,7 +25490,7 @@
         <v>142</v>
       </c>
       <c r="G829" t="n">
-        <v>137.02</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="830">
@@ -25738,7 +25738,7 @@
         <v>2.95</v>
       </c>
       <c r="G837" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="838">
@@ -25800,7 +25800,7 @@
         <v>2.95</v>
       </c>
       <c r="G839" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="840">
@@ -26482,7 +26482,7 @@
         <v>241.17</v>
       </c>
       <c r="G861" t="n">
-        <v>209.87</v>
+        <v>211.09</v>
       </c>
     </row>
     <row r="862">
@@ -26606,7 +26606,7 @@
         <v>2.67</v>
       </c>
       <c r="G865" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="866">
@@ -26730,7 +26730,7 @@
         <v>2.67</v>
       </c>
       <c r="G869" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="870">
@@ -28306,7 +28306,7 @@
         <v>0.47</v>
       </c>
       <c r="G921" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="922">
@@ -29046,7 +29046,7 @@
         <v>6.05</v>
       </c>
       <c r="G945" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="946">
@@ -29654,7 +29654,7 @@
         <v>1.24</v>
       </c>
       <c r="G965" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="966">
@@ -29927,7 +29927,7 @@
         <v>3.22</v>
       </c>
       <c r="G974" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="975">
@@ -30018,7 +30018,7 @@
         <v>3.22</v>
       </c>
       <c r="G977" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="978">
@@ -30200,7 +30200,7 @@
         <v>0.91</v>
       </c>
       <c r="G983" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="984">
@@ -30655,7 +30655,7 @@
         <v>6.34</v>
       </c>
       <c r="G998" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="999">
@@ -30837,7 +30837,7 @@
         <v>12.79</v>
       </c>
       <c r="G1004" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="1005">
@@ -30928,7 +30928,7 @@
         <v>10.54</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="1008">
@@ -32190,7 +32190,7 @@
         <v>1.94</v>
       </c>
       <c r="G1049" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="1050">
@@ -36997,7 +36997,7 @@
         <v>1.21</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="1209">
@@ -38175,7 +38175,7 @@
         <v>1.24</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="1247">
@@ -39932,7 +39932,7 @@
         <v>1.09</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="1304">
@@ -40490,7 +40490,7 @@
         <v>2.33</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="1322">
@@ -40738,7 +40738,7 @@
         <v>2.49</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="1330">
@@ -40862,7 +40862,7 @@
         <v>0.39</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="1334">
@@ -42206,7 +42206,7 @@
         <v>27.91</v>
       </c>
       <c r="G1377" t="n">
-        <v>6.4</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="1378">
@@ -42268,7 +42268,7 @@
         <v>26.5</v>
       </c>
       <c r="G1379" t="n">
-        <v>6.85</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="1380">
@@ -42330,7 +42330,7 @@
         <v>76.89</v>
       </c>
       <c r="G1381" t="n">
-        <v>49.19</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="1382">
@@ -42392,7 +42392,7 @@
         <v>37.94</v>
       </c>
       <c r="G1383" t="n">
-        <v>15.23</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="1384">

--- a/data/processed/san_data.xlsx
+++ b/data/processed/san_data.xlsx
@@ -557,7 +557,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>17.41</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>44.93</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="7">
@@ -743,7 +743,7 @@
         <v>110</v>
       </c>
       <c r="G10" t="n">
-        <v>41.16</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +805,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>25.91</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="13">
@@ -929,7 +929,7 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>29.48</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="17">
@@ -991,7 +991,7 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>10.85</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="19">
@@ -1115,7 +1115,7 @@
         <v>220</v>
       </c>
       <c r="G22" t="n">
-        <v>63.57</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="23">
@@ -1177,7 +1177,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="25">
@@ -1239,7 +1239,7 @@
         <v>170</v>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="27">
@@ -1301,7 +1301,7 @@
         <v>100</v>
       </c>
       <c r="G28" t="n">
-        <v>41.53</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="29">
@@ -1425,7 +1425,7 @@
         <v>120</v>
       </c>
       <c r="G32" t="n">
-        <v>36.03</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="33">
@@ -1611,7 +1611,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="n">
-        <v>18.57</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="39">
@@ -1673,7 +1673,7 @@
         <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>34.26</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="41">
@@ -1797,7 +1797,7 @@
         <v>90</v>
       </c>
       <c r="G44" t="n">
-        <v>27.82</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="45">
@@ -3207,7 +3207,7 @@
         <v>1.12</v>
       </c>
       <c r="G90" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="91">
@@ -3331,7 +3331,7 @@
         <v>0.6</v>
       </c>
       <c r="G94" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="95">
@@ -5345,7 +5345,7 @@
         <v>84.31</v>
       </c>
       <c r="G160" t="n">
-        <v>79.64</v>
+        <v>79.70999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -5407,7 +5407,7 @@
         <v>84.31</v>
       </c>
       <c r="G162" t="n">
-        <v>80.59</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="163">
@@ -5531,7 +5531,7 @@
         <v>45.39</v>
       </c>
       <c r="G166" t="n">
-        <v>37.94</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="167">
@@ -6259,7 +6259,7 @@
         <v>0.29</v>
       </c>
       <c r="G190" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="191">
@@ -8057,7 +8057,7 @@
         <v>9.15</v>
       </c>
       <c r="G248" t="n">
-        <v>7.99</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -9235,7 +9235,7 @@
         <v>11.45</v>
       </c>
       <c r="G286" t="n">
-        <v>10.12</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="287">
@@ -9297,7 +9297,7 @@
         <v>11.68</v>
       </c>
       <c r="G288" t="n">
-        <v>10.03</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="289">
@@ -10818,7 +10818,7 @@
         <v>18.18</v>
       </c>
       <c r="G337" t="n">
-        <v>13.37</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="338">
@@ -10880,7 +10880,7 @@
         <v>34.93</v>
       </c>
       <c r="G339" t="n">
-        <v>12.95</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="340">
@@ -11066,7 +11066,7 @@
         <v>34.74</v>
       </c>
       <c r="G345" t="n">
-        <v>28.2</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="346">
@@ -11128,7 +11128,7 @@
         <v>25.49</v>
       </c>
       <c r="G347" t="n">
-        <v>21.02</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="348">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="G357" t="n">
         <v>0.16</v>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="G359" t="n">
         <v>0.07000000000000001</v>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="G361" t="n">
         <v>0.78</v>
@@ -12812,7 +12812,7 @@
         <v>2.43</v>
       </c>
       <c r="G407" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="408">
@@ -12936,7 +12936,7 @@
         <v>1.52</v>
       </c>
       <c r="G411" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="412">
@@ -13122,7 +13122,7 @@
         <v>3.69</v>
       </c>
       <c r="G417" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="418">
@@ -13308,7 +13308,7 @@
         <v>634.95</v>
       </c>
       <c r="G423" t="n">
-        <v>380.44</v>
+        <v>383.25</v>
       </c>
     </row>
     <row r="424">
@@ -13432,7 +13432,7 @@
         <v>662.95</v>
       </c>
       <c r="G427" t="n">
-        <v>536.6</v>
+        <v>605.8200000000001</v>
       </c>
     </row>
     <row r="428">
@@ -13494,7 +13494,7 @@
         <v>23.32</v>
       </c>
       <c r="G429" t="n">
-        <v>15.06</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="430">
@@ -14300,7 +14300,7 @@
         <v>4.47</v>
       </c>
       <c r="G455" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="456">
@@ -14486,7 +14486,7 @@
         <v>601.73</v>
       </c>
       <c r="G461" t="n">
-        <v>581.72</v>
+        <v>581.73</v>
       </c>
     </row>
     <row r="462">
@@ -14672,7 +14672,7 @@
         <v>18.65</v>
       </c>
       <c r="G467" t="n">
-        <v>16.63</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="468">
@@ -14734,7 +14734,7 @@
         <v>18.68</v>
       </c>
       <c r="G469" t="n">
-        <v>16.56</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="470">
@@ -14982,7 +14982,7 @@
         <v>80.05</v>
       </c>
       <c r="G477" t="n">
-        <v>38.68</v>
+        <v>38.72</v>
       </c>
     </row>
     <row r="478">
@@ -15041,10 +15041,10 @@
         </is>
       </c>
       <c r="F479" t="n">
-        <v>48.05</v>
+        <v>72.05</v>
       </c>
       <c r="G479" t="n">
-        <v>8.789999999999999</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="480">
@@ -15106,7 +15106,7 @@
         <v>42.05</v>
       </c>
       <c r="G481" t="n">
-        <v>16.2</v>
+        <v>16.21</v>
       </c>
     </row>
     <row r="482">
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="F483" t="n">
-        <v>30.05</v>
+        <v>54.05</v>
       </c>
       <c r="G483" t="n">
-        <v>8.08</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="484">
@@ -15577,7 +15577,7 @@
         <v>293.95</v>
       </c>
       <c r="G496" t="n">
-        <v>284.15</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="497">
@@ -15825,7 +15825,7 @@
         <v>291.95</v>
       </c>
       <c r="G504" t="n">
-        <v>280.05</v>
+        <v>280.09</v>
       </c>
     </row>
     <row r="505">
@@ -20403,7 +20403,7 @@
         <v>15.5</v>
       </c>
       <c r="G650" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="651">
@@ -20498,7 +20498,7 @@
         <v>15.5</v>
       </c>
       <c r="G653" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="654">
@@ -20965,7 +20965,7 @@
         <v>8</v>
       </c>
       <c r="G668" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="669">
@@ -21060,7 +21060,7 @@
         <v>8</v>
       </c>
       <c r="G671" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="672">
@@ -21713,7 +21713,7 @@
         <v>20</v>
       </c>
       <c r="G692" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="693">
@@ -21746,7 +21746,7 @@
         <v>20</v>
       </c>
       <c r="G693" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="694">
@@ -21808,7 +21808,7 @@
         <v>20</v>
       </c>
       <c r="G695" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="696">
@@ -21841,7 +21841,7 @@
         <v>20</v>
       </c>
       <c r="G696" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="697">
@@ -21903,7 +21903,7 @@
         <v>20</v>
       </c>
       <c r="G698" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="699">
@@ -21936,7 +21936,7 @@
         <v>20</v>
       </c>
       <c r="G699" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="700">
@@ -23238,7 +23238,7 @@
         <v>24</v>
       </c>
       <c r="G741" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="742">
@@ -23333,7 +23333,7 @@
         <v>24</v>
       </c>
       <c r="G744" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="745">
@@ -24048,7 +24048,7 @@
         <v>8</v>
       </c>
       <c r="G767" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="768">
@@ -24110,7 +24110,7 @@
         <v>8</v>
       </c>
       <c r="G769" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="770">
@@ -25201,7 +25201,7 @@
         <v>108</v>
       </c>
       <c r="G804" t="n">
-        <v>36.13</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="805">
@@ -25234,7 +25234,7 @@
         <v>108</v>
       </c>
       <c r="G805" t="n">
-        <v>50.8</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="806">
@@ -25296,7 +25296,7 @@
         <v>108</v>
       </c>
       <c r="G807" t="n">
-        <v>36.13</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="808">
@@ -25329,7 +25329,7 @@
         <v>108</v>
       </c>
       <c r="G808" t="n">
-        <v>50.8</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="809">
@@ -25391,7 +25391,7 @@
         <v>108</v>
       </c>
       <c r="G810" t="n">
-        <v>36.13</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="811">
@@ -25424,7 +25424,7 @@
         <v>108</v>
       </c>
       <c r="G811" t="n">
-        <v>50.8</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="812">
@@ -25486,7 +25486,7 @@
         <v>12</v>
       </c>
       <c r="G813" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="814">
@@ -25581,7 +25581,7 @@
         <v>12</v>
       </c>
       <c r="G816" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="817">
@@ -25676,7 +25676,7 @@
         <v>12</v>
       </c>
       <c r="G819" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="820">
@@ -28189,7 +28189,7 @@
         <v>12</v>
       </c>
       <c r="G900" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="901">
@@ -28222,7 +28222,7 @@
         <v>16</v>
       </c>
       <c r="G901" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="902">
@@ -28284,7 +28284,7 @@
         <v>12</v>
       </c>
       <c r="G903" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="904">
@@ -28317,7 +28317,7 @@
         <v>16</v>
       </c>
       <c r="G904" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="905">
@@ -28379,7 +28379,7 @@
         <v>12</v>
       </c>
       <c r="G906" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="907">
@@ -28412,7 +28412,7 @@
         <v>16</v>
       </c>
       <c r="G907" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="908">
@@ -30148,7 +30148,7 @@
         <v>10.49</v>
       </c>
       <c r="G963" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="964">
@@ -30181,7 +30181,7 @@
         <v>12</v>
       </c>
       <c r="G964" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="965">
@@ -30243,7 +30243,7 @@
         <v>10.49</v>
       </c>
       <c r="G966" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="967">
@@ -30276,7 +30276,7 @@
         <v>12</v>
       </c>
       <c r="G967" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="968">
@@ -32367,7 +32367,7 @@
         <v>2.27</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="1035">
@@ -32739,7 +32739,7 @@
         <v>1.35</v>
       </c>
       <c r="G1046" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="1047">
@@ -32801,7 +32801,7 @@
         <v>1.38</v>
       </c>
       <c r="G1048" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="1049">
@@ -35208,10 +35208,10 @@
         </is>
       </c>
       <c r="F1126" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G1126" t="n">
-        <v>137.29</v>
+        <v>142.54</v>
       </c>
     </row>
     <row r="1127">
@@ -35270,10 +35270,10 @@
         </is>
       </c>
       <c r="F1128" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G1128" t="n">
-        <v>136</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="1129">
@@ -35332,10 +35332,10 @@
         </is>
       </c>
       <c r="F1130" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G1130" t="n">
-        <v>135.61</v>
+        <v>141.13</v>
       </c>
     </row>
     <row r="1131">
@@ -35394,10 +35394,10 @@
         </is>
       </c>
       <c r="F1132" t="n">
-        <v>142.86</v>
+        <v>148.86</v>
       </c>
       <c r="G1132" t="n">
-        <v>139.64</v>
+        <v>144.76</v>
       </c>
     </row>
     <row r="1133">
@@ -35456,10 +35456,10 @@
         </is>
       </c>
       <c r="F1134" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G1134" t="n">
-        <v>137.09</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="1135">
@@ -35831,7 +35831,7 @@
         <v>45.17</v>
       </c>
       <c r="G1146" t="n">
-        <v>13.43</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="1147">
@@ -35893,7 +35893,7 @@
         <v>45.17</v>
       </c>
       <c r="G1148" t="n">
-        <v>13.43</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="1149">
@@ -36451,7 +36451,7 @@
         <v>241.17</v>
       </c>
       <c r="G1166" t="n">
-        <v>212.28</v>
+        <v>212.31</v>
       </c>
     </row>
     <row r="1167">
@@ -37567,7 +37567,7 @@
         <v>2.29</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1203">
@@ -38473,7 +38473,7 @@
         <v>0.47</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="1233">
@@ -39155,7 +39155,7 @@
         <v>6.05</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="1255">
@@ -39279,7 +39279,7 @@
         <v>6.05</v>
       </c>
       <c r="G1258" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="1259">
@@ -39899,7 +39899,7 @@
         <v>12.79</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="1279">
@@ -40023,7 +40023,7 @@
         <v>12.79</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.35</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="1283">
@@ -41015,7 +41015,7 @@
         <v>3.81</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="1315">
@@ -41201,7 +41201,7 @@
         <v>1.94</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="1321">
@@ -41635,7 +41635,7 @@
         <v>12.79</v>
       </c>
       <c r="G1334" t="n">
-        <v>8.529999999999999</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="1335">
@@ -41697,7 +41697,7 @@
         <v>12.79</v>
       </c>
       <c r="G1336" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="1337">
@@ -41759,7 +41759,7 @@
         <v>10.54</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="1339">
@@ -41821,7 +41821,7 @@
         <v>10.54</v>
       </c>
       <c r="G1340" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="1341">
@@ -42627,7 +42627,7 @@
         <v>1.01</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1367">
@@ -42689,7 +42689,7 @@
         <v>1.01</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="1369">
@@ -43185,7 +43185,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="1385">
@@ -43309,7 +43309,7 @@
         <v>0.91</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="1389">
@@ -43805,7 +43805,7 @@
         <v>17.87</v>
       </c>
       <c r="G1404" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="1405">
@@ -44549,7 +44549,7 @@
         <v>1</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="1429">
@@ -44611,7 +44611,7 @@
         <v>1.03</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="1431">
@@ -46343,7 +46343,7 @@
         <v>241.17</v>
       </c>
       <c r="G1486" t="n">
-        <v>208.85</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="1487">
@@ -46405,7 +46405,7 @@
         <v>241.17</v>
       </c>
       <c r="G1488" t="n">
-        <v>208.85</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="1489">
@@ -49282,7 +49282,7 @@
         <v>1.31</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="1582">
@@ -51576,7 +51576,7 @@
         <v>1.24</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="1656">
@@ -53581,7 +53581,7 @@
         <v>0.27</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="1721">
@@ -53891,7 +53891,7 @@
         <v>2.33</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="1731">
@@ -55871,7 +55871,7 @@
         <v>27.91</v>
       </c>
       <c r="G1794" t="n">
-        <v>5.33</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="1795">
@@ -55933,7 +55933,7 @@
         <v>26.5</v>
       </c>
       <c r="G1796" t="n">
-        <v>7.03</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="1797">
@@ -55992,10 +55992,10 @@
         </is>
       </c>
       <c r="F1798" t="n">
-        <v>76.89</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="G1798" t="n">
-        <v>60.06</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="1799">
@@ -56054,10 +56054,10 @@
         </is>
       </c>
       <c r="F1800" t="n">
-        <v>37.94</v>
+        <v>42.04</v>
       </c>
       <c r="G1800" t="n">
-        <v>15.76</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="1801">
@@ -56243,7 +56243,7 @@
         <v>27.91</v>
       </c>
       <c r="G1806" t="n">
-        <v>22.76</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="1807">
@@ -56305,7 +56305,7 @@
         <v>26.5</v>
       </c>
       <c r="G1808" t="n">
-        <v>7.08</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="1809">
@@ -56364,10 +56364,10 @@
         </is>
       </c>
       <c r="F1810" t="n">
-        <v>76.89</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="G1810" t="n">
-        <v>60.57</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="1811">
@@ -56426,10 +56426,10 @@
         </is>
       </c>
       <c r="F1812" t="n">
-        <v>37.94</v>
+        <v>42.04</v>
       </c>
       <c r="G1812" t="n">
-        <v>16.55</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="1813">
